--- a/Atomberg_Home_App_Test_Cases.xlsx
+++ b/Atomberg_Home_App_Test_Cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rohit Bhagat\Documents\AtombergApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A543137B-46DC-4AF1-9D34-4F0910FD816D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27737B71-ECBF-4F94-9CA0-115016FE2799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="668">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -2040,6 +2040,9 @@
   </si>
   <si>
     <t>Open a section →  Retry</t>
+  </si>
+  <si>
+    <t>Description / Title</t>
   </si>
 </sst>
 </file>
@@ -2537,10 +2540,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>667</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>260</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
